--- a/20260701职务分工.xlsx
+++ b/20260701职务分工.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexwei/Developer/Shanghaitech-HSPP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ants\Desktop\社会实践\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48EC277-70E7-8049-BFF5-F31D4E89F724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80505A24-6FF5-4599-AF53-A634915CE2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="600" windowWidth="25600" windowHeight="16260" xr2:uid="{CD52326A-4C25-EA42-96B3-ACD8376A7190}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{CD52326A-4C25-EA42-96B3-ACD8376A7190}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>调研组</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>顾原弘</t>
-  </si>
-  <si>
-    <t>陈伊诺</t>
   </si>
   <si>
     <t>杨泊宁</t>
@@ -225,7 +222,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -328,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -352,6 +349,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,9 +651,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -691,7 +691,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -797,7 +797,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -939,7 +939,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -947,15 +947,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDD945A-0B8A-4E44-B4D7-684C7296CEF6}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.81640625" style="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -966,18 +966,18 @@
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -986,36 +986,36 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -1031,9 +1031,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
@@ -1043,15 +1043,15 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
@@ -1061,70 +1061,70 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -1135,9 +1135,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1146,10 +1146,10 @@
         <v>2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
@@ -1160,10 +1160,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -1174,13 +1174,11 @@
         <v>6</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1188,10 +1186,10 @@
         <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1199,7 +1197,16 @@
         <v>13</v>
       </c>
     </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="8"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E16:F16"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">

--- a/20260701职务分工.xlsx
+++ b/20260701职务分工.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ants\Desktop\社会实践\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80505A24-6FF5-4599-AF53-A634915CE2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B113EAE3-D41D-44C2-9988-5ECF435D7A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{CD52326A-4C25-EA42-96B3-ACD8376A7190}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
